--- a/data/student-loan.xlsx
+++ b/data/student-loan.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I2"/>
+  <dimension ref="A1:I1"/>
   <cols>
     <col min="1" max="1" width="20.83203125" customWidth="1"/>
     <col min="2" max="2" width="30.83203125" customWidth="1"/>
@@ -439,38 +439,9 @@
         <v>notes</v>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="str">
-        <v>fed-loan</v>
-      </c>
-      <c r="B2" t="str">
-        <v>Federal Student Loan</v>
-      </c>
-      <c r="C2" t="str">
-        <v>Fixed 10yr</v>
-      </c>
-      <c r="D2">
-        <v>28000</v>
-      </c>
-      <c r="E2">
-        <v>18200</v>
-      </c>
-      <c r="F2">
-        <v>4.5</v>
-      </c>
-      <c r="G2">
-        <v>290</v>
-      </c>
-      <c r="H2" t="str">
-        <v>2032-06-01</v>
-      </c>
-      <c r="I2" t="str">
-        <v>Direct unsubsidized. Standard repayment plan.</v>
-      </c>
-    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:I2"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:I1"/>
   </ignoredErrors>
 </worksheet>
 </file>